--- a/TestData/DataFile.xlsx
+++ b/TestData/DataFile.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piyun\OneDrive\Desktop\Trainings\SA5078Java-Selenium\SeleniumMaven\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EBD3BF-2953-46F6-A6AA-88F1C5E475EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9634979B-3D5D-4B59-9568-DB16049FEEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookData" sheetId="1" r:id="rId1"/>
+    <sheet name="LoginData" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>BookId</t>
   </si>
@@ -43,6 +44,27 @@
   </si>
   <si>
     <t>Playwright</t>
+  </si>
+  <si>
+    <t>UserName</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>admin123</t>
+  </si>
+  <si>
+    <t>Riya</t>
+  </si>
+  <si>
+    <t>test123</t>
+  </si>
+  <si>
+    <t>Sarang</t>
   </si>
 </sst>
 </file>
@@ -457,4 +479,58 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0281604A-1047-4E85-A7CF-375B4699E41F}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.109375" customWidth="1"/>
+    <col min="2" max="2" width="31.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>